--- a/reports/pdf_change_20260702.xlsx
+++ b/reports/pdf_change_20260702.xlsx
@@ -575,7 +575,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,782억      당일 2026-07-02  vs  전영업일 2026-07-01      매수 4종목  /  매도 4종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 6,036억      당일 2026-07-02  vs  전영업일 2026-07-01      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -671,10 +671,10 @@
         <v>33</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1750458600</v>
+        <v>1762308900</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>0.303</v>
+        <v>0.292</v>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
@@ -690,10 +690,10 @@
         <v>-36</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-490984560</v>
+        <v>-494308440</v>
       </c>
       <c r="J6" s="16" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.082</v>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>31</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>589152520</v>
+        <v>593140980</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>0.102</v>
+        <v>0.098</v>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
@@ -730,10 +730,10 @@
         <v>-24</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2307888000</v>
+        <v>-2323512000</v>
       </c>
       <c r="J7" s="16" t="n">
-        <v>-0.399</v>
+        <v>-0.385</v>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
@@ -751,10 +751,10 @@
         <v>10</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1721610000</v>
+        <v>1733265000</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>0.298</v>
+        <v>0.287</v>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
         <v>-20</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-2744236000</v>
+        <v>-2762814000</v>
       </c>
       <c r="J8" s="16" t="n">
-        <v>-0.475</v>
+        <v>-0.458</v>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
         <v>6</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>504385200</v>
+        <v>507799800</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
         <v>-6</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-512450400</v>
+        <v>-515919600</v>
       </c>
       <c r="J9" s="16" t="n">
-        <v>-0.089</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,784억      당일 2026-07-02  vs  전영업일 2026-07-01      매수 2종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,954억      당일 2026-07-02  vs  전영업일 2026-07-01      매수 2종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -920,10 +920,10 @@
         <v>68</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>472247760</v>
+        <v>473916480</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.099</v>
+        <v>0.096</v>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         <v>-20</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1890440000</v>
+        <v>-1897120000</v>
       </c>
       <c r="J14" s="16" t="n">
-        <v>-0.395</v>
+        <v>-0.383</v>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
@@ -960,10 +960,10 @@
         <v>6</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1433112000</v>
+        <v>1438176000</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,651억      당일 2026-07-02  vs  전영업일 2026-07-01      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,774억      당일 2026-07-02  vs  전영업일 2026-07-01      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -1003,7 +1003,7 @@
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,801억      당일 2026-07-02  vs  전영업일 2026-07-01      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,898억      당일 2026-07-02  vs  전영업일 2026-07-01      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -1027,7 +1027,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 376억      당일 2026-07-02  vs  전영업일 2026-07-01      매수 4종목  /  매도 4종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 394억      당일 2026-07-02  vs  전영업일 2026-07-01      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1123,10 +1123,10 @@
         <v>23</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>105931100</v>
+        <v>102660500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>0.281</v>
+        <v>0.26</v>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         <v>-76</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-140193400</v>
+        <v>-168412200</v>
       </c>
       <c r="J26" s="16" t="n">
-        <v>-0.372</v>
+        <v>-0.427</v>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         <v>7</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>92959300</v>
+        <v>91576800</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>0.247</v>
+        <v>0.232</v>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>-13</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-35636900</v>
+        <v>-37331450</v>
       </c>
       <c r="J27" s="16" t="n">
         <v>-0.095</v>
@@ -1203,10 +1203,10 @@
         <v>5</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>20382000</v>
+        <v>21843500</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>0.054</v>
+        <v>0.055</v>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
@@ -1222,10 +1222,10 @@
         <v>-9</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-37327500</v>
+        <v>-40100400</v>
       </c>
       <c r="J28" s="16" t="n">
-        <v>-0.099</v>
+        <v>-0.102</v>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
@@ -1243,10 +1243,10 @@
         <v>4</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>115498000</v>
+        <v>106966000</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>0.307</v>
+        <v>0.271</v>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
@@ -1262,10 +1262,10 @@
         <v>-4</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-46989200</v>
+        <v>-49706800</v>
       </c>
       <c r="J29" s="16" t="n">
-        <v>-0.125</v>
+        <v>-0.126</v>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 613억      당일 2026-07-02  vs  전영업일 2026-07-01      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 639억      당일 2026-07-02  vs  전영업일 2026-07-01      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
